--- a/Sources/دورة احمال محولات هندسة مدينة كفر الشيخ شهر 3 -2-1 (2026).xlsx
+++ b/Sources/دورة احمال محولات هندسة مدينة كفر الشيخ شهر 3 -2-1 (2026).xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Global\Desktop\NDEDC_Production\Sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC1B459-CAE8-48E2-943E-F3935FCD4539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="450" windowWidth="20400" windowHeight="7740"/>
+    <workbookView xWindow="-120" yWindow="330" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="مدينة كفر الشيخ" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'مدينة كفر الشيخ'!$A$1:$Y$518</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1876,7 +1877,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2975,6 +2976,50 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
@@ -3011,14 +3056,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="15" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection hidden="1"/>
@@ -3030,42 +3067,6 @@
     <xf numFmtId="1" fontId="15" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3127,11 +3128,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="13">
     <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3145,6 +3151,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -3152,391 +3165,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3876,7 +3505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3914,110 +3543,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="151" t="s">
+      <c r="C1" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="153" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="154"/>
-      <c r="F1" s="151" t="s">
+      <c r="D1" s="144" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="145"/>
+      <c r="F1" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="151" t="s">
+      <c r="H1" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="151" t="s">
+      <c r="J1" s="139" t="s">
         <v>590</v>
       </c>
-      <c r="K1" s="144" t="s">
+      <c r="K1" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="144" t="s">
+      <c r="L1" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="144" t="s">
+      <c r="M1" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="144" t="s">
+      <c r="N1" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="144" t="s">
+      <c r="O1" s="137" t="s">
         <v>571</v>
       </c>
-      <c r="P1" s="156" t="s">
+      <c r="P1" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="156" t="s">
+      <c r="Q1" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="156" t="s">
+      <c r="R1" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="144" t="s">
+      <c r="S1" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="144" t="s">
+      <c r="T1" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="144" t="s">
+      <c r="U1" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="144" t="s">
+      <c r="V1" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="144" t="s">
+      <c r="W1" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="144" t="s">
+      <c r="X1" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="156" t="s">
+      <c r="Y1" s="135" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="150"/>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
+    <row r="2" spans="1:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="143"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="145"/>
-      <c r="T2" s="145"/>
-      <c r="U2" s="145"/>
-      <c r="V2" s="145"/>
-      <c r="W2" s="145"/>
-      <c r="X2" s="145"/>
-      <c r="Y2" s="157"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="136"/>
+      <c r="Q2" s="136"/>
+      <c r="R2" s="136"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="136"/>
     </row>
     <row r="3" spans="1:29" s="49" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="83">
@@ -20367,13 +19996,13 @@
         <v>1500</v>
       </c>
       <c r="O194" s="118"/>
-      <c r="P194" s="138" t="s">
+      <c r="P194" s="149" t="s">
         <v>120</v>
       </c>
-      <c r="Q194" s="139"/>
-      <c r="R194" s="139"/>
-      <c r="S194" s="139"/>
-      <c r="T194" s="140"/>
+      <c r="Q194" s="150"/>
+      <c r="R194" s="150"/>
+      <c r="S194" s="150"/>
+      <c r="T194" s="151"/>
       <c r="U194" s="100" t="e">
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
@@ -20437,13 +20066,13 @@
         <v>1000</v>
       </c>
       <c r="O195" s="118"/>
-      <c r="P195" s="138" t="s">
+      <c r="P195" s="149" t="s">
         <v>120</v>
       </c>
-      <c r="Q195" s="139"/>
-      <c r="R195" s="139"/>
-      <c r="S195" s="139"/>
-      <c r="T195" s="140"/>
+      <c r="Q195" s="150"/>
+      <c r="R195" s="150"/>
+      <c r="S195" s="150"/>
+      <c r="T195" s="151"/>
       <c r="U195" s="100" t="e">
         <f t="shared" si="55"/>
         <v>#DIV/0!</v>
@@ -25945,12 +25574,12 @@
       <c r="N261" s="47">
         <v>500</v>
       </c>
-      <c r="O261" s="146" t="s">
+      <c r="O261" s="155" t="s">
         <v>548</v>
       </c>
-      <c r="P261" s="147"/>
-      <c r="Q261" s="147"/>
-      <c r="R261" s="148"/>
+      <c r="P261" s="156"/>
+      <c r="Q261" s="156"/>
+      <c r="R261" s="157"/>
       <c r="S261" s="48">
         <f t="shared" si="81"/>
         <v>720</v>
@@ -35475,13 +35104,13 @@
         <v>500</v>
       </c>
       <c r="O374" s="43"/>
-      <c r="P374" s="141" t="s">
+      <c r="P374" s="152" t="s">
         <v>548</v>
       </c>
-      <c r="Q374" s="142"/>
-      <c r="R374" s="142"/>
-      <c r="S374" s="142"/>
-      <c r="T374" s="143"/>
+      <c r="Q374" s="153"/>
+      <c r="R374" s="153"/>
+      <c r="S374" s="153"/>
+      <c r="T374" s="154"/>
       <c r="U374" s="44" t="e">
         <f t="shared" si="106"/>
         <v>#DIV/0!</v>
@@ -37649,13 +37278,13 @@
         <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P400" s="141" t="s">
+      <c r="P400" s="152" t="s">
         <v>548</v>
       </c>
-      <c r="Q400" s="142"/>
-      <c r="R400" s="142"/>
-      <c r="S400" s="142"/>
-      <c r="T400" s="143"/>
+      <c r="Q400" s="153"/>
+      <c r="R400" s="153"/>
+      <c r="S400" s="153"/>
+      <c r="T400" s="154"/>
       <c r="U400" s="44" t="e">
         <f t="shared" si="121"/>
         <v>#DIV/0!</v>
@@ -43721,13 +43350,13 @@
         <f t="shared" si="138"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P474" s="135" t="s">
+      <c r="P474" s="146" t="s">
         <v>120</v>
       </c>
-      <c r="Q474" s="136"/>
-      <c r="R474" s="136"/>
-      <c r="S474" s="136"/>
-      <c r="T474" s="137"/>
+      <c r="Q474" s="147"/>
+      <c r="R474" s="147"/>
+      <c r="S474" s="147"/>
+      <c r="T474" s="148"/>
       <c r="U474" s="44" t="e">
         <f t="shared" si="145"/>
         <v>#DIV/0!</v>
@@ -46508,10 +46137,28 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertColumns="0" insertRows="0" deleteColumns="0" deleteRows="0" autoFilter="0"/>
-  <autoFilter ref="A1:Y518">
+  <autoFilter ref="A1:Y518" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="3" showButton="0"/>
   </autoFilter>
   <mergeCells count="30">
+    <mergeCell ref="P474:T474"/>
+    <mergeCell ref="P195:T195"/>
+    <mergeCell ref="P374:T374"/>
+    <mergeCell ref="P400:T400"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="P194:T194"/>
+    <mergeCell ref="O261:R261"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -46524,52 +46171,34 @@
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
     <mergeCell ref="X1:X2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="P474:T474"/>
-    <mergeCell ref="P195:T195"/>
-    <mergeCell ref="P374:T374"/>
-    <mergeCell ref="P400:T400"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="P194:T194"/>
-    <mergeCell ref="O261:R261"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:G474">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>IF(V3&gt;80,"true","false")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>IF(V3&gt;89,"true","false")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>IF(V3=0,"true","false")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>IF(V3&lt;50,"true","false")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G475:G517">
-    <cfRule type="expression" dxfId="39" priority="824">
+    <cfRule type="expression" dxfId="8" priority="824">
       <formula>IF(U475&gt;89,"true","false")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="825">
+    <cfRule type="expression" dxfId="7" priority="825">
       <formula>IF(U475=0,"true","false")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="826">
+    <cfRule type="expression" dxfId="6" priority="826">
       <formula>IF(U475&lt;50,"true","false")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:U517">
-    <cfRule type="cellIs" dxfId="36" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46579,7 +46208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -48190,7 +47819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -51964,178 +51593,23 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="T2:T6">
-    <cfRule type="cellIs" dxfId="35" priority="160" operator="greaterThan">
-      <formula>80</formula>
+  <conditionalFormatting sqref="F2:F61">
+    <cfRule type="expression" dxfId="4" priority="830">
+      <formula>IF(#REF!&lt;50,"true","false")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T7">
-    <cfRule type="cellIs" dxfId="34" priority="155" operator="greaterThan">
-      <formula>80</formula>
+    <cfRule type="expression" dxfId="3" priority="828">
+      <formula>IF(#REF!&gt;89,"true","false")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T12">
-    <cfRule type="cellIs" dxfId="33" priority="150" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T13">
-    <cfRule type="cellIs" dxfId="32" priority="145" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T14">
-    <cfRule type="cellIs" dxfId="31" priority="140" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T15">
-    <cfRule type="cellIs" dxfId="30" priority="135" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T16">
-    <cfRule type="cellIs" dxfId="29" priority="130" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T17">
-    <cfRule type="cellIs" dxfId="28" priority="125" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T18">
-    <cfRule type="cellIs" dxfId="27" priority="120" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T19">
-    <cfRule type="cellIs" dxfId="26" priority="115" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T20">
-    <cfRule type="cellIs" dxfId="25" priority="110" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T21">
-    <cfRule type="cellIs" dxfId="24" priority="105" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T22">
-    <cfRule type="cellIs" dxfId="23" priority="100" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T23:T26">
-    <cfRule type="cellIs" dxfId="22" priority="95" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T27">
-    <cfRule type="cellIs" dxfId="21" priority="90" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T28">
-    <cfRule type="cellIs" dxfId="20" priority="85" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T29:T31">
-    <cfRule type="cellIs" dxfId="19" priority="80" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T32">
-    <cfRule type="cellIs" dxfId="18" priority="75" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T33">
-    <cfRule type="cellIs" dxfId="17" priority="70" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T34">
-    <cfRule type="cellIs" dxfId="16" priority="65" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T35:T36">
-    <cfRule type="cellIs" dxfId="15" priority="60" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T37">
-    <cfRule type="cellIs" dxfId="14" priority="55" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T38">
-    <cfRule type="cellIs" dxfId="13" priority="50" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T39:T41">
-    <cfRule type="cellIs" dxfId="12" priority="45" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T42">
-    <cfRule type="cellIs" dxfId="11" priority="40" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T43">
-    <cfRule type="cellIs" dxfId="10" priority="35" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T44:T45">
-    <cfRule type="cellIs" dxfId="9" priority="30" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T46">
-    <cfRule type="cellIs" dxfId="8" priority="25" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T47">
-    <cfRule type="cellIs" dxfId="7" priority="20" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T48:T52">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T53:T60">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T61">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F61">
-    <cfRule type="expression" dxfId="3" priority="827">
+    <cfRule type="expression" dxfId="2" priority="827">
       <formula>IF(#REF!&gt;80,"true","false")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="828">
-      <formula>IF(#REF!&gt;89,"true","false")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="829">
       <formula>IF(#REF!=0,"true","false")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="830">
-      <formula>IF(#REF!&lt;50,"true","false")</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T61">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThan">
+      <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
